--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -5549,8 +5549,16 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>120.50</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n">
         <v>20586</v>
       </c>
@@ -5585,8 +5593,16 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>502.00</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="n">
         <v>3474</v>
       </c>
@@ -5613,8 +5629,16 @@
           <t>鈊象</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>761.00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+32.0</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n">
         <v>3264</v>
       </c>
@@ -5653,8 +5677,16 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+11.0</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="n">
         <v>2655</v>
       </c>
@@ -5693,8 +5725,16 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>188.50</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n">
         <v>2594</v>
       </c>
@@ -5721,8 +5761,16 @@
           <t>尼克森</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>68.30</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="n">
         <v>1161</v>
       </c>
@@ -5757,8 +5805,16 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>61.20</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+1.9</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="n">
         <v>1106</v>
       </c>
@@ -5793,8 +5849,16 @@
           <t>擎邦</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>58.20</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="n">
         <v>701</v>
       </c>
@@ -5833,8 +5897,16 @@
           <t>鈦昇</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>184.00</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="n">
         <v>700</v>
       </c>
@@ -5865,8 +5937,16 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n">
         <v>699</v>
       </c>
@@ -5893,8 +5973,16 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>511.00</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+14.0</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="n">
         <v>678</v>
       </c>
@@ -5925,8 +6013,16 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>114.00</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n">
         <v>673</v>
       </c>
@@ -5957,8 +6053,16 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="n">
         <v>660</v>
       </c>
@@ -5989,8 +6093,16 @@
           <t>安勤</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>136.00</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n">
         <v>557</v>
       </c>
@@ -6025,8 +6137,16 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>53.80</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+2.3</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="n">
         <v>502</v>
       </c>
@@ -6057,8 +6177,16 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>67.90</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+1.8</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n">
         <v>462</v>
       </c>
@@ -6085,8 +6213,16 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>258.00</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+14.0</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n">
         <v>455</v>
       </c>
@@ -6117,8 +6253,16 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>73.70</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n">
         <v>451</v>
       </c>
@@ -6145,8 +6289,16 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>146.00</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="n">
         <v>443</v>
       </c>
@@ -6173,8 +6325,16 @@
           <t>陽程</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>214.00</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+15.0</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n">
         <v>379</v>
       </c>
@@ -6205,8 +6365,16 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n">
         <v>363</v>
       </c>
@@ -6237,8 +6405,16 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>398.00</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>-12.5</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="n">
         <v>361</v>
       </c>
@@ -6265,8 +6441,16 @@
           <t>擎亞</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>84.60</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+0.7</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="n">
         <v>344</v>
       </c>
@@ -6293,8 +6477,16 @@
           <t>雷笛克光學</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>23.30</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="n">
         <v>321</v>
       </c>
@@ -6329,8 +6521,16 @@
           <t>M31</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>515.00</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+38.5</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="n">
         <v>309</v>
       </c>
@@ -6365,8 +6565,16 @@
           <t>好德</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>34.25</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+3.1</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="n">
         <v>299</v>
       </c>
@@ -6393,8 +6601,16 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>72.80</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+2.6</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n">
         <v>297</v>
       </c>
@@ -6425,8 +6641,16 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>1710.00</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>+115.0</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n">
         <v>275</v>
       </c>
@@ -6457,8 +6681,16 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>86.40</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n">
         <v>263</v>
       </c>
@@ -6489,8 +6721,16 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>135.50</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n">
         <v>261</v>
       </c>
@@ -6517,8 +6757,16 @@
           <t>宜特</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n">
         <v>231</v>
       </c>
@@ -6545,8 +6793,16 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>52.50</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n">
         <v>218</v>
       </c>
@@ -6577,8 +6833,16 @@
           <t>先進光</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>173.00</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n">
         <v>212</v>
       </c>
@@ -6605,8 +6869,16 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>241.50</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n">
         <v>204</v>
       </c>
@@ -6633,8 +6905,16 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>43.00</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>+0.85</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="n">
         <v>201</v>
       </c>
@@ -6665,8 +6945,16 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>505.00</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>+40.0</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="n">
         <v>191</v>
       </c>
@@ -6693,8 +6981,16 @@
           <t>越峰</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>+2.75</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n">
         <v>189</v>
       </c>
@@ -6725,8 +7021,16 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>68.60</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="n">
         <v>186</v>
       </c>
@@ -6757,8 +7061,16 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>542.00</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>+14.0</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="n">
         <v>176</v>
       </c>
@@ -6785,8 +7097,16 @@
           <t>均豪</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>107.00</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="n">
         <v>167</v>
       </c>
@@ -6813,8 +7133,16 @@
           <t>邑昇</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>57.30</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n">
         <v>164</v>
       </c>
@@ -6841,8 +7169,16 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>129.50</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="n">
         <v>152</v>
       </c>
@@ -6869,8 +7205,16 @@
           <t>信立</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>34.05</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n">
         <v>150</v>
       </c>
@@ -6897,8 +7241,16 @@
           <t>蜜望實</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>133.00</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n">
         <v>148</v>
       </c>
@@ -6925,8 +7277,16 @@
           <t>美琪瑪</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>77.40</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>+2.1</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n">
         <v>147</v>
       </c>
@@ -6957,8 +7317,16 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>41.40</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n">
         <v>140</v>
       </c>
@@ -6989,8 +7357,16 @@
           <t>久正</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n">
         <v>130</v>
       </c>
@@ -7021,8 +7397,16 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>85.70</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>+1.1</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="n">
         <v>128</v>
       </c>
@@ -7053,8 +7437,16 @@
           <t>廣穎</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>134.00</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="n">
         <v>126</v>
       </c>
@@ -7081,8 +7473,16 @@
           <t>泰藝</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr"/>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>44.75</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n">
         <v>122</v>
       </c>
@@ -7109,8 +7509,16 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="n">
         <v>115</v>
       </c>
@@ -7137,8 +7545,16 @@
           <t>群翊</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>358.50</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>+12.5</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n">
         <v>112</v>
       </c>
@@ -7169,8 +7585,16 @@
           <t>濱川</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>64.70</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>+1.4</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n">
         <v>111</v>
       </c>
@@ -7201,8 +7625,16 @@
           <t>廣運</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>48.60</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n">
         <v>106</v>
       </c>
@@ -7233,8 +7665,16 @@
           <t>雍智科技</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>1520.00</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>-35.0</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n">
         <v>104</v>
       </c>
@@ -7261,8 +7701,16 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>44.95</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n">
         <v>103</v>
       </c>
@@ -7293,8 +7741,16 @@
           <t>廣寰科</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>41.05</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n">
         <v>100</v>
       </c>
@@ -7325,8 +7781,16 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>652.00</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>+9.0</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n">
         <v>95</v>
       </c>
@@ -7353,8 +7817,16 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>47.55</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n">
         <v>95</v>
       </c>
@@ -7385,8 +7857,16 @@
           <t>精剛</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n">
         <v>92</v>
       </c>
@@ -7417,8 +7897,16 @@
           <t>宸曜</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>212.00</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n">
         <v>91</v>
       </c>
@@ -7445,8 +7933,16 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2700.00</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>+20.0</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n">
         <v>88</v>
       </c>
@@ -7473,8 +7969,16 @@
           <t>全宇昕</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
-      <c r="F66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>149.50</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="n">
         <v>87</v>
       </c>
@@ -7505,8 +8009,16 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
-      <c r="F67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>43.10</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="n">
         <v>85</v>
       </c>
@@ -7533,8 +8045,16 @@
           <t>巨有科技</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>306.50</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n">
         <v>80</v>
       </c>
@@ -7565,8 +8085,16 @@
           <t>其陽</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
-      <c r="F69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>49.45</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>+1.35</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n">
         <v>77</v>
       </c>
@@ -7597,8 +8125,16 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr"/>
-      <c r="F70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n">
         <v>76</v>
       </c>
@@ -7629,8 +8165,16 @@
           <t>松上</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
-      <c r="F71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="n">
         <v>74</v>
       </c>
@@ -7661,8 +8205,16 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>37.85</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n">
         <v>74</v>
       </c>
@@ -7689,8 +8241,16 @@
           <t>博大</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>132.00</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n">
         <v>74</v>
       </c>
@@ -7721,8 +8281,16 @@
           <t>艾華</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr"/>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>107.50</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>+9.5</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n">
         <v>73</v>
       </c>
@@ -7749,8 +8317,16 @@
           <t>佳邦</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
-      <c r="F75" s="4" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>74.30</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n">
         <v>73</v>
       </c>
@@ -7781,8 +8357,16 @@
           <t>亞昕</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>20.80</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n">
         <v>72</v>
       </c>
@@ -7813,8 +8397,16 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
-      <c r="F77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>27.30</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n">
         <v>69</v>
       </c>
@@ -7841,8 +8433,16 @@
           <t>力致</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
-      <c r="F78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>77.50</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>+0.9</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n">
         <v>68</v>
       </c>
@@ -7869,8 +8469,16 @@
           <t>弘塑</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
-      <c r="F79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>2410.00</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>+45.0</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n">
         <v>66</v>
       </c>
@@ -7897,8 +8505,16 @@
           <t>倍微</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>29.70</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="n">
         <v>64</v>
       </c>
@@ -7929,8 +8545,16 @@
           <t>光譜</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr"/>
-      <c r="F81" s="4" t="inlineStr"/>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>23.25</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="n">
         <v>63</v>
       </c>
@@ -7957,8 +8581,16 @@
           <t>青雲</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
-      <c r="F82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>285.00</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="n">
         <v>63</v>
       </c>
@@ -7985,8 +8617,16 @@
           <t>能率網通</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
-      <c r="F83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>21.90</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="n">
         <v>62</v>
       </c>
@@ -8013,8 +8653,16 @@
           <t>德宏</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
-      <c r="F84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>181.00</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="n">
         <v>60</v>
       </c>
@@ -8041,8 +8689,16 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr"/>
-      <c r="F85" s="4" t="inlineStr"/>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>61.50</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="n">
         <v>58</v>
       </c>
@@ -8069,8 +8725,16 @@
           <t>茂達</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr"/>
-      <c r="F86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>279.00</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>+4.5</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="n">
         <v>57</v>
       </c>
@@ -8097,8 +8761,16 @@
           <t>長佳智能</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr"/>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>53.70</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="n">
         <v>55</v>
       </c>
@@ -8129,8 +8801,16 @@
           <t>迅德</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr"/>
-      <c r="F88" s="4" t="inlineStr"/>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>+1.3</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="n">
         <v>54</v>
       </c>
@@ -8161,8 +8841,16 @@
           <t>信紘科</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr"/>
-      <c r="F89" s="4" t="inlineStr"/>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>261.50</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="n">
         <v>54</v>
       </c>
@@ -8189,8 +8877,16 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
-      <c r="F90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>45.45</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="n">
         <v>52</v>
       </c>
@@ -8217,8 +8913,16 @@
           <t>港建*</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>44.80</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="n">
         <v>50</v>
       </c>
@@ -8249,8 +8953,16 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr"/>
-      <c r="F92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>47.80</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="n">
         <v>49</v>
       </c>
@@ -8281,8 +8993,16 @@
           <t>振曜</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
-      <c r="F93" s="4" t="inlineStr"/>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>81.50</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>+0.3</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="n">
         <v>48</v>
       </c>
@@ -8309,8 +9029,16 @@
           <t>朋億*</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
-      <c r="F94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>270.50</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="n">
         <v>48</v>
       </c>
@@ -8341,8 +9069,16 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
-      <c r="F95" s="4" t="inlineStr"/>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>181.00</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="n">
         <v>47</v>
       </c>
@@ -8373,8 +9109,16 @@
           <t>福裕</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr"/>
-      <c r="F96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>16.45</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="n">
         <v>47</v>
       </c>
@@ -8405,8 +9149,16 @@
           <t>兆利</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>77.10</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="n">
         <v>46</v>
       </c>
@@ -8437,8 +9189,16 @@
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr"/>
-      <c r="F98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>572.00</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="n">
         <v>46</v>
       </c>
@@ -8465,8 +9225,16 @@
           <t>東浦</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
-      <c r="F99" s="4" t="inlineStr"/>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>46.25</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="n">
         <v>45</v>
       </c>
@@ -8493,8 +9261,16 @@
           <t>尚立</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr"/>
-      <c r="F100" s="4" t="inlineStr"/>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>15.05</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="n">
         <v>45</v>
       </c>
@@ -8521,8 +9297,16 @@
           <t>光聚晶電</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
-      <c r="F101" s="4" t="inlineStr"/>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>+0.75</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="n">
         <v>44</v>
       </c>
@@ -8549,8 +9333,16 @@
           <t>杰力</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr"/>
-      <c r="F102" s="4" t="inlineStr"/>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>101.50</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="n">
         <v>43</v>
       </c>
@@ -8581,8 +9373,16 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
-      <c r="F103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>99.70</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="n">
         <v>42</v>
       </c>
@@ -8713,8 +9513,16 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
-      <c r="F109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>116.00</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="n">
         <v>-9944</v>
       </c>
@@ -8741,8 +9549,16 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
-      <c r="F110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>246.00</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="n">
         <v>-4467</v>
       </c>
@@ -8769,8 +9585,16 @@
           <t>寶雅*</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
-      <c r="F111" s="4" t="inlineStr"/>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>69.30</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n">
         <v>-4342</v>
       </c>
@@ -8801,8 +9625,16 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr"/>
-      <c r="F112" s="4" t="inlineStr"/>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>449.00</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-23.0</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="n">
         <v>-3280</v>
       </c>
@@ -8833,8 +9665,16 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr"/>
-      <c r="F113" s="4" t="inlineStr"/>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>948.00</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="n">
         <v>-2611</v>
       </c>
@@ -8861,8 +9701,16 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr"/>
-      <c r="F114" s="4" t="inlineStr"/>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>378.00</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="n">
         <v>-2207</v>
       </c>
@@ -8889,8 +9737,16 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr"/>
-      <c r="F115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>108.00</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="n">
         <v>-2186</v>
       </c>
@@ -8921,8 +9777,16 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr"/>
-      <c r="F116" s="4" t="inlineStr"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>+6.0</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="n">
         <v>-2070</v>
       </c>
@@ -8949,8 +9813,16 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
-      <c r="F117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>94.50</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="n">
         <v>-1923</v>
       </c>
@@ -8977,8 +9849,16 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr"/>
-      <c r="F118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>563.00</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>-27.0</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n">
         <v>-1680</v>
       </c>
@@ -9005,8 +9885,16 @@
           <t>英濟</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
-      <c r="F119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>33.65</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="n">
         <v>-1607</v>
       </c>
@@ -9045,8 +9933,16 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>2125.00</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="n">
         <v>-1587</v>
       </c>
@@ -9077,8 +9973,16 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
-      <c r="F121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>209.50</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>+12.5</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="n">
         <v>-1526</v>
       </c>
@@ -9117,8 +10021,16 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr"/>
-      <c r="F122" s="4" t="inlineStr"/>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>+0.4</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="n">
         <v>-1485</v>
       </c>
@@ -9149,8 +10061,16 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr"/>
-      <c r="F123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>32.45</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="n">
         <v>-1135</v>
       </c>
@@ -9189,8 +10109,16 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr"/>
-      <c r="F124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>94.50</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>+3.4</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="n">
         <v>-1042</v>
       </c>
@@ -9229,8 +10157,16 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr"/>
-      <c r="F125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>36.80</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="n">
         <v>-964</v>
       </c>
@@ -9261,8 +10197,16 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr"/>
-      <c r="F126" s="4" t="inlineStr"/>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>36.60</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="n">
         <v>-893</v>
       </c>
@@ -9293,8 +10237,16 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
-      <c r="F127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="n">
         <v>-810</v>
       </c>
@@ -9325,8 +10277,16 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr"/>
-      <c r="F128" s="4" t="inlineStr"/>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="n">
         <v>-795</v>
       </c>
@@ -9353,8 +10313,16 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
-      <c r="F129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>139.00</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>+6.0</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="n">
         <v>-757</v>
       </c>
@@ -9385,8 +10353,16 @@
           <t>高端疫苗</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>59.80</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="n">
         <v>-736</v>
       </c>
@@ -9413,8 +10389,16 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
-      <c r="F131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>23.60</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="n">
         <v>-625</v>
       </c>
@@ -9441,8 +10425,16 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>30.95</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="n">
         <v>-612</v>
       </c>
@@ -9469,8 +10461,16 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
-      <c r="F133" s="4" t="inlineStr"/>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>1495.00</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>+35.0</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="n">
         <v>-576</v>
       </c>
@@ -9497,8 +10497,16 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr"/>
-      <c r="F134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>49.10</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="n">
         <v>-569</v>
       </c>
@@ -9525,8 +10533,16 @@
           <t>立碁</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr"/>
-      <c r="F135" s="4" t="inlineStr"/>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>76.40</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>+2.3</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="n">
         <v>-559</v>
       </c>
@@ -9553,8 +10569,16 @@
           <t>力士</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr"/>
-      <c r="F136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>64.00</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n">
         <v>-524</v>
       </c>
@@ -9589,8 +10613,16 @@
           <t>泰谷</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr"/>
-      <c r="F137" s="4" t="inlineStr"/>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>47.20</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>+0.25</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n">
         <v>-507</v>
       </c>
@@ -9617,8 +10649,16 @@
           <t>驊訊</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr"/>
-      <c r="F138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>37.00</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n">
         <v>-506</v>
       </c>
@@ -9653,8 +10693,16 @@
           <t>同致</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr"/>
-      <c r="F139" s="4" t="inlineStr"/>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>45.40</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>+2.35</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n">
         <v>-428</v>
       </c>
@@ -9681,8 +10729,16 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr"/>
-      <c r="F140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>62.10</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="n">
         <v>-414</v>
       </c>
@@ -9709,8 +10765,16 @@
           <t>科嶠</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
-      <c r="F141" s="4" t="inlineStr"/>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>328.00</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="n">
         <v>-333</v>
       </c>
@@ -9737,8 +10801,16 @@
           <t>營邦</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr"/>
-      <c r="F142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>729.00</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="n">
         <v>-314</v>
       </c>
@@ -9765,8 +10837,16 @@
           <t>博智</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
-      <c r="F143" s="4" t="inlineStr"/>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>336.00</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="n">
         <v>-308</v>
       </c>
@@ -9797,8 +10877,16 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>178.00</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>+8.0</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="n">
         <v>-300</v>
       </c>
@@ -9825,8 +10913,16 @@
           <t>宣德</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="n">
         <v>-279</v>
       </c>
@@ -9853,8 +10949,16 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr"/>
-      <c r="F146" s="4" t="inlineStr"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>54.00</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="n">
         <v>-271</v>
       </c>
@@ -9885,8 +10989,16 @@
           <t>華宏</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
-      <c r="F147" s="4" t="inlineStr"/>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>52.00</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="n">
         <v>-263</v>
       </c>
@@ -9917,8 +11029,16 @@
           <t>晶呈科技</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>325.00</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="n">
         <v>-259</v>
       </c>
@@ -9953,8 +11073,16 @@
           <t>碩禾</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
-      <c r="F149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>121.00</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="n">
         <v>-241</v>
       </c>
@@ -9981,8 +11109,16 @@
           <t>安可</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr"/>
-      <c r="F150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>37.90</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="n">
         <v>-227</v>
       </c>
@@ -10009,8 +11145,16 @@
           <t>驊宏資</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
-      <c r="F151" s="4" t="inlineStr"/>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>39.20</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>+1.85</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="n">
         <v>-214</v>
       </c>
@@ -10037,8 +11181,16 @@
           <t>伍豐</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr"/>
-      <c r="F152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>21.70</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="n">
         <v>-197</v>
       </c>
@@ -10069,8 +11221,16 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
-      <c r="F153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>378.50</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="n">
         <v>-196</v>
       </c>
@@ -10097,8 +11257,16 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>1555.00</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>-10.0</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="n">
         <v>-187</v>
       </c>
@@ -10125,8 +11293,16 @@
           <t>健喬</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
-      <c r="F155" s="4" t="inlineStr"/>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="n">
         <v>-187</v>
       </c>
@@ -10153,8 +11329,16 @@
           <t>世界</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>170.50</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="n">
         <v>-184</v>
       </c>
@@ -10181,8 +11365,16 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
-      <c r="F157" s="4" t="inlineStr"/>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>71.30</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="n">
         <v>-180</v>
       </c>
@@ -10209,8 +11401,16 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>5415.00</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>-205.0</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="n">
         <v>-173</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -26801,16 +26801,8 @@
           <t>欣銓</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>284.00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>+15.5</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="n">
         <v>1968</v>
       </c>
@@ -26834,16 +26826,8 @@
           <t>順達</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>387.50</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>+19.5</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="n">
         <v>1813</v>
       </c>
@@ -26867,16 +26851,8 @@
           <t>康和證</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>23.65</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>+0.65</t>
-        </is>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="n">
         <v>1498</v>
       </c>
@@ -26900,16 +26876,8 @@
           <t>濱川</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>61.00</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>+5.5</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="n">
         <v>1272</v>
       </c>
@@ -26933,16 +26901,8 @@
           <t>致和證</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>36.65</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="n">
         <v>1199</v>
       </c>
@@ -26966,16 +26926,8 @@
           <t>福邦證</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>15.80</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="n">
         <v>1161</v>
       </c>
@@ -26999,16 +26951,8 @@
           <t>宏遠證</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="n">
         <v>1092</v>
       </c>
@@ -27032,16 +26976,8 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>389.00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>nannan</t>
-        </is>
-      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="n">
         <v>826</v>
       </c>
@@ -27065,16 +27001,8 @@
           <t>立端</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>88.40</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+2.8</t>
-        </is>
-      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="n">
         <v>810</v>
       </c>
@@ -27098,16 +27026,8 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>618.00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>+7.0</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="n">
         <v>801</v>
       </c>
@@ -27131,16 +27051,8 @@
           <t>家登</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>548.00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+15.0</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="n">
         <v>774</v>
       </c>
@@ -27164,16 +27076,8 @@
           <t>台嘉碩</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>48.65</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>+1.15</t>
-        </is>
-      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="n">
         <v>762</v>
       </c>
@@ -27197,16 +27101,8 @@
           <t>單井</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>45.20</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>+0.85</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="n">
         <v>698</v>
       </c>
@@ -27230,16 +27126,8 @@
           <t>泰谷</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>48.50</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>+3.15</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="n">
         <v>677</v>
       </c>
@@ -27263,16 +27151,8 @@
           <t>大甲</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>+12.5</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="n">
         <v>674</v>
       </c>
@@ -27296,16 +27176,8 @@
           <t>富強鑫</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>28.75</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="n">
         <v>660</v>
       </c>
@@ -27329,16 +27201,8 @@
           <t>聯光通</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>41.35</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+3.75</t>
-        </is>
-      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="n">
         <v>654</v>
       </c>
@@ -27362,16 +27226,8 @@
           <t>富喬</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>121.00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="n">
         <v>620</v>
       </c>
@@ -27395,16 +27251,8 @@
           <t>萬泰科</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>70.20</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
       <c r="G22" s="4" t="n">
         <v>620</v>
       </c>
@@ -27428,16 +27276,8 @@
           <t>智通*</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>94.90</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="n">
         <v>599</v>
       </c>
@@ -27461,16 +27301,8 @@
           <t>群聯</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>2150.00</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>+10.0</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="n">
         <v>576</v>
       </c>
@@ -27494,16 +27326,8 @@
           <t>慶騰</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>+2.9</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="n">
         <v>546</v>
       </c>
@@ -27527,16 +27351,8 @@
           <t>漢磊</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>63.40</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="n">
         <v>538</v>
       </c>
@@ -27560,16 +27376,8 @@
           <t>台半</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>93.30</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="n">
         <v>526</v>
       </c>
@@ -27593,16 +27401,8 @@
           <t>九豪</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>48.90</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="n">
         <v>501</v>
       </c>
@@ -27626,16 +27426,8 @@
           <t>倚強科</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>98.70</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>+8.9</t>
-        </is>
-      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="n">
         <v>463</v>
       </c>
@@ -27659,16 +27451,8 @@
           <t>永捷</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>12.45</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>+0.35</t>
-        </is>
-      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="n">
         <v>448</v>
       </c>
@@ -27692,16 +27476,8 @@
           <t>宣德</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="n">
         <v>447</v>
       </c>
@@ -27725,16 +27501,8 @@
           <t>華電網</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="n">
         <v>445</v>
       </c>
@@ -27758,16 +27526,8 @@
           <t>合一</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>44.75</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="n">
         <v>431</v>
       </c>
@@ -27791,16 +27551,8 @@
           <t>金居</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>491.50</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="n">
         <v>409</v>
       </c>
@@ -27824,16 +27576,8 @@
           <t>旭然</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>87.30</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>+4.1</t>
-        </is>
-      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="n">
         <v>402</v>
       </c>
@@ -27857,16 +27601,8 @@
           <t>僑威</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>46.20</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
       <c r="G36" s="4" t="n">
         <v>395</v>
       </c>
@@ -27890,16 +27626,8 @@
           <t>國統</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>52.40</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="n">
         <v>391</v>
       </c>
@@ -27923,16 +27651,8 @@
           <t>聚和</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>47.20</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
       <c r="G38" s="4" t="n">
         <v>388</v>
       </c>
@@ -27956,16 +27676,8 @@
           <t>力麒</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>7.74</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>+0.25</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="n">
         <v>386</v>
       </c>
@@ -27989,16 +27701,8 @@
           <t>正德</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+0.2</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="n">
         <v>381</v>
       </c>
@@ -28022,16 +27726,8 @@
           <t>中裕</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>64.10</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="n">
         <v>379</v>
       </c>
@@ -28055,16 +27751,8 @@
           <t>友威科</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>100.50</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>+3.7</t>
-        </is>
-      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
       <c r="G42" s="4" t="n">
         <v>371</v>
       </c>
@@ -28088,16 +27776,8 @@
           <t>風青</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>54.00</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="n">
         <v>360</v>
       </c>
@@ -28121,16 +27801,8 @@
           <t>豪勉</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>67.70</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>+6.1</t>
-        </is>
-      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="n">
         <v>352</v>
       </c>
@@ -28154,16 +27826,8 @@
           <t>艾訊</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="n">
         <v>321</v>
       </c>
@@ -28187,16 +27851,8 @@
           <t>廣積</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>59.10</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="n">
         <v>303</v>
       </c>
@@ -28220,16 +27876,8 @@
           <t>元大期</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>87.90</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>+0.4</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="n">
         <v>296</v>
       </c>
@@ -28253,16 +27901,8 @@
           <t>立敦</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>71.40</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>+1.7</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
       <c r="G48" s="4" t="n">
         <v>288</v>
       </c>
@@ -28286,16 +27926,8 @@
           <t>振發</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="n">
         <v>273</v>
       </c>
@@ -28319,16 +27951,8 @@
           <t>科嶠</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>302.50</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>+27.5</t>
-        </is>
-      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="n">
         <v>258</v>
       </c>
@@ -28352,16 +27976,8 @@
           <t>安國</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>84.90</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="n">
         <v>255</v>
       </c>
@@ -28385,16 +28001,8 @@
           <t>安碁</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>44.30</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="n">
         <v>250</v>
       </c>
@@ -28418,16 +28026,8 @@
           <t>鑫科</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>62.10</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="n">
         <v>229</v>
       </c>
@@ -28451,16 +28051,8 @@
           <t>台星科</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>181.00</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
       <c r="G54" s="4" t="n">
         <v>228</v>
       </c>
@@ -28484,16 +28076,8 @@
           <t>營邦</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>702.00</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="n">
         <v>227</v>
       </c>
@@ -28517,16 +28101,8 @@
           <t>網家</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>24.05</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
       <c r="G56" s="4" t="n">
         <v>221</v>
       </c>
@@ -28550,16 +28126,8 @@
           <t>律勝</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>30.40</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="n">
         <v>217</v>
       </c>
@@ -28583,16 +28151,8 @@
           <t>亞電</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>78.80</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="n">
         <v>217</v>
       </c>
@@ -28616,16 +28176,8 @@
           <t>瑞耘</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="n">
         <v>216</v>
       </c>
@@ -28649,16 +28201,8 @@
           <t>高鋒</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>44.50</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="n">
         <v>213</v>
       </c>
@@ -28682,16 +28226,8 @@
           <t>東洋</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>79.10</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>+0.7</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="n">
         <v>210</v>
       </c>
@@ -28715,16 +28251,8 @@
           <t>加高</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="n">
         <v>210</v>
       </c>
@@ -28748,16 +28276,8 @@
           <t>新潤</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="n">
         <v>206</v>
       </c>
@@ -28781,16 +28301,8 @@
           <t>曜越</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="n">
         <v>204</v>
       </c>
@@ -28814,16 +28326,8 @@
           <t>浩鼎</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>29.90</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>+2.7</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="n">
         <v>201</v>
       </c>
@@ -28847,16 +28351,8 @@
           <t>三聯</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>91.50</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>+4.6</t>
-        </is>
-      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="n">
         <v>187</v>
       </c>
@@ -28880,16 +28376,8 @@
           <t>倉和</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>426.50</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>+38.5</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="n">
         <v>184</v>
       </c>
@@ -28913,16 +28401,8 @@
           <t>雙鴻</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>1520.00</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+40.0</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="n">
         <v>181</v>
       </c>
@@ -28946,16 +28426,8 @@
           <t>全宇昕</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>154.00</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>+7.5</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="n">
         <v>181</v>
       </c>
@@ -28979,16 +28451,8 @@
           <t>聯一光</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>177.50</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>-8.0</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
       <c r="G70" s="4" t="n">
         <v>180</v>
       </c>
@@ -29012,16 +28476,8 @@
           <t>安勤</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>131.50</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="n">
         <v>161</v>
       </c>
@@ -29045,16 +28501,8 @@
           <t>信昌電</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>308.00</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>-6.0</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
       <c r="G72" s="4" t="n">
         <v>159</v>
       </c>
@@ -29078,16 +28526,8 @@
           <t>松瑞藥</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="n">
         <v>157</v>
       </c>
@@ -29111,16 +28551,8 @@
           <t>北基</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>+0.75</t>
-        </is>
-      </c>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="n">
         <v>151</v>
       </c>
@@ -29144,16 +28576,8 @@
           <t>宸曜</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>206.50</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>+18.5</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="n">
         <v>149</v>
       </c>
@@ -29177,16 +28601,8 @@
           <t>佶優</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>27.90</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="n">
         <v>145</v>
       </c>
@@ -29210,16 +28626,8 @@
           <t>茂綸</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>132.00</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
       <c r="G77" s="4" t="n">
         <v>137</v>
       </c>
@@ -29243,16 +28651,8 @@
           <t>擎邦</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>51.70</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E78" s="4" t="inlineStr"/>
+      <c r="F78" s="4" t="inlineStr"/>
       <c r="G78" s="4" t="n">
         <v>131</v>
       </c>
@@ -29276,16 +28676,8 @@
           <t>奇鈦科</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>106.00</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>+2.5</t>
-        </is>
-      </c>
+      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="inlineStr"/>
       <c r="G79" s="4" t="n">
         <v>130</v>
       </c>
@@ -29309,16 +28701,8 @@
           <t>千如</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>43.65</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+0.3</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="n">
         <v>127</v>
       </c>
@@ -29342,16 +28726,8 @@
           <t>廣寰科</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>42.10</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="4" t="inlineStr"/>
       <c r="G81" s="4" t="n">
         <v>124</v>
       </c>
@@ -29375,16 +28751,8 @@
           <t>由田</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>256.50</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
       <c r="G82" s="4" t="n">
         <v>116</v>
       </c>
@@ -29408,16 +28776,8 @@
           <t>系統電</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>52.10</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
       <c r="G83" s="4" t="n">
         <v>116</v>
       </c>
@@ -29441,16 +28801,8 @@
           <t>廣錠</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>+2.25</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="4" t="inlineStr"/>
       <c r="G84" s="4" t="n">
         <v>116</v>
       </c>
@@ -29474,16 +28826,8 @@
           <t>公準</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>75.90</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>+6.9</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="n">
         <v>114</v>
       </c>
@@ -29507,16 +28851,8 @@
           <t>大立</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>16.90</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="4" t="inlineStr"/>
       <c r="G86" s="4" t="n">
         <v>110</v>
       </c>
@@ -29540,16 +28876,8 @@
           <t>美琪瑪</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>75.50</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="n">
         <v>110</v>
       </c>
@@ -29573,16 +28901,8 @@
           <t>晟德</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="4" t="inlineStr"/>
       <c r="G88" s="4" t="n">
         <v>109</v>
       </c>
@@ -29606,16 +28926,8 @@
           <t>萬旭</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>29.50</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="n">
         <v>106</v>
       </c>
@@ -29639,16 +28951,8 @@
           <t>元創精密</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="4" t="inlineStr"/>
       <c r="G90" s="4" t="n">
         <v>104</v>
       </c>
@@ -29672,16 +28976,8 @@
           <t>聯上</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>15.55</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="n">
         <v>103</v>
       </c>
@@ -29705,16 +29001,8 @@
           <t>德晉</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="4" t="inlineStr"/>
       <c r="G92" s="4" t="n">
         <v>102</v>
       </c>
@@ -29738,16 +29026,8 @@
           <t>欣厚-KY</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>17.05</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>+1.55</t>
-        </is>
-      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="n">
         <v>96</v>
       </c>
@@ -29771,16 +29051,8 @@
           <t>光環</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>178.50</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="n">
         <v>95</v>
       </c>
@@ -29804,16 +29076,8 @@
           <t>旭品</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>12.30</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="inlineStr"/>
       <c r="G95" s="4" t="n">
         <v>93</v>
       </c>
@@ -29837,16 +29101,8 @@
           <t>元山</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>46.00</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>+0.9</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr"/>
       <c r="G96" s="4" t="n">
         <v>93</v>
       </c>
@@ -29870,16 +29126,8 @@
           <t>晟楠</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="inlineStr"/>
       <c r="G97" s="4" t="n">
         <v>90</v>
       </c>
@@ -29903,16 +29151,8 @@
           <t>岳豐</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>+0.1</t>
-        </is>
-      </c>
+      <c r="E98" s="4" t="inlineStr"/>
+      <c r="F98" s="4" t="inlineStr"/>
       <c r="G98" s="4" t="n">
         <v>89</v>
       </c>
@@ -29936,16 +29176,8 @@
           <t>保勝光學</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>66.20</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>+1.2</t>
-        </is>
-      </c>
+      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="inlineStr"/>
       <c r="G99" s="4" t="n">
         <v>88</v>
       </c>
@@ -29969,16 +29201,8 @@
           <t>坤悅</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>22.80</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E100" s="4" t="inlineStr"/>
+      <c r="F100" s="4" t="inlineStr"/>
       <c r="G100" s="4" t="n">
         <v>87</v>
       </c>
@@ -30002,16 +29226,8 @@
           <t>堡達</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>53.90</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>+0.6</t>
-        </is>
-      </c>
+      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="inlineStr"/>
       <c r="G101" s="4" t="n">
         <v>83</v>
       </c>
@@ -30035,16 +29251,8 @@
           <t>神盾</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>98.70</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>+1.6</t>
-        </is>
-      </c>
+      <c r="E102" s="4" t="inlineStr"/>
+      <c r="F102" s="4" t="inlineStr"/>
       <c r="G102" s="4" t="n">
         <v>83</v>
       </c>
@@ -30068,16 +29276,8 @@
           <t>龍巖</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>49.05</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="inlineStr"/>
       <c r="G103" s="4" t="n">
         <v>81</v>
       </c>
@@ -30178,16 +29378,8 @@
           <t>世紀*</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>nannan</t>
-        </is>
-      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr"/>
       <c r="G109" s="4" t="n">
         <v>-9560</v>
       </c>
@@ -30211,16 +29403,8 @@
           <t>頎邦</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>224.00</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr"/>
       <c r="G110" s="4" t="n">
         <v>-9060</v>
       </c>
@@ -30244,16 +29428,8 @@
           <t>合晶</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>115.00</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="inlineStr"/>
       <c r="G111" s="4" t="n">
         <v>-5880</v>
       </c>
@@ -30277,16 +29453,8 @@
           <t>鈺創</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>109.50</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>-4.0</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
+      <c r="F112" s="4" t="inlineStr"/>
       <c r="G112" s="4" t="n">
         <v>-3610</v>
       </c>
@@ -30310,16 +29478,8 @@
           <t>茂迪</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr"/>
       <c r="G113" s="4" t="n">
         <v>-2662</v>
       </c>
@@ -30343,16 +29503,8 @@
           <t>穩懋</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>490.50</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
+      <c r="E114" s="4" t="inlineStr"/>
+      <c r="F114" s="4" t="inlineStr"/>
       <c r="G114" s="4" t="n">
         <v>-2247</v>
       </c>
@@ -30376,16 +29528,8 @@
           <t>亞通</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>37.35</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr"/>
       <c r="G115" s="4" t="n">
         <v>-1848</v>
       </c>
@@ -30409,16 +29553,8 @@
           <t>長科*</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>73.30</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E116" s="4" t="inlineStr"/>
+      <c r="F116" s="4" t="inlineStr"/>
       <c r="G116" s="4" t="n">
         <v>-1765</v>
       </c>
@@ -30442,16 +29578,8 @@
           <t>環球晶</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>931.00</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>-13.0</t>
-        </is>
-      </c>
+      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="inlineStr"/>
       <c r="G117" s="4" t="n">
         <v>-1373</v>
       </c>
@@ -30475,16 +29603,8 @@
           <t>光頡</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>132.50</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>+6.5</t>
-        </is>
-      </c>
+      <c r="E118" s="4" t="inlineStr"/>
+      <c r="F118" s="4" t="inlineStr"/>
       <c r="G118" s="4" t="n">
         <v>-1348</v>
       </c>
@@ -30508,16 +29628,8 @@
           <t>台燿</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>1435.00</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>+65.0</t>
-        </is>
-      </c>
+      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="inlineStr"/>
       <c r="G119" s="4" t="n">
         <v>-1037</v>
       </c>
@@ -30541,16 +29653,8 @@
           <t>良維</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>281.00</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E120" s="4" t="inlineStr"/>
+      <c r="F120" s="4" t="inlineStr"/>
       <c r="G120" s="4" t="n">
         <v>-946</v>
       </c>
@@ -30574,16 +29678,8 @@
           <t>中探針</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>175.50</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="inlineStr"/>
       <c r="G121" s="4" t="n">
         <v>-938</v>
       </c>
@@ -30607,16 +29703,8 @@
           <t>雷科</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>117.00</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="n">
         <v>-917</v>
       </c>
@@ -30640,16 +29728,8 @@
           <t>晶宏</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>92.80</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>-0.9</t>
-        </is>
-      </c>
+      <c r="E123" s="4" t="inlineStr"/>
+      <c r="F123" s="4" t="inlineStr"/>
       <c r="G123" s="4" t="n">
         <v>-838</v>
       </c>
@@ -30673,16 +29753,8 @@
           <t>東捷</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>138.00</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E124" s="4" t="inlineStr"/>
+      <c r="F124" s="4" t="inlineStr"/>
       <c r="G124" s="4" t="n">
         <v>-833</v>
       </c>
@@ -30706,16 +29778,8 @@
           <t>世禾</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>186.50</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E125" s="4" t="inlineStr"/>
+      <c r="F125" s="4" t="inlineStr"/>
       <c r="G125" s="4" t="n">
         <v>-831</v>
       </c>
@@ -30739,16 +29803,8 @@
           <t>上詮</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>661.00</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>-22.0</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="n">
         <v>-718</v>
       </c>
@@ -30772,16 +29828,8 @@
           <t>新盛力</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>239.50</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>+2.0</t>
-        </is>
-      </c>
+      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="inlineStr"/>
       <c r="G127" s="4" t="n">
         <v>-701</v>
       </c>
@@ -30805,16 +29853,8 @@
           <t>精材</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>443.00</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E128" s="4" t="inlineStr"/>
+      <c r="F128" s="4" t="inlineStr"/>
       <c r="G128" s="4" t="n">
         <v>-678</v>
       </c>
@@ -30838,16 +29878,8 @@
           <t>中美晶</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>186.50</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="inlineStr"/>
       <c r="G129" s="4" t="n">
         <v>-632</v>
       </c>
@@ -30871,16 +29903,8 @@
           <t>天品</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>114.50</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>+1.5</t>
-        </is>
-      </c>
+      <c r="E130" s="4" t="inlineStr"/>
+      <c r="F130" s="4" t="inlineStr"/>
       <c r="G130" s="4" t="n">
         <v>-587</v>
       </c>
@@ -30904,16 +29928,8 @@
           <t>華容</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>52.30</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>-0.8</t>
-        </is>
-      </c>
+      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="inlineStr"/>
       <c r="G131" s="4" t="n">
         <v>-493</v>
       </c>
@@ -30937,16 +29953,8 @@
           <t>宏捷科</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>109.50</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E132" s="4" t="inlineStr"/>
+      <c r="F132" s="4" t="inlineStr"/>
       <c r="G132" s="4" t="n">
         <v>-458</v>
       </c>
@@ -30970,16 +29978,8 @@
           <t>高僑</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>42.35</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t>+3.85</t>
-        </is>
-      </c>
+      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="inlineStr"/>
       <c r="G133" s="4" t="n">
         <v>-453</v>
       </c>
@@ -31003,16 +30003,8 @@
           <t>驊宏資</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>+0.15</t>
-        </is>
-      </c>
+      <c r="E134" s="4" t="inlineStr"/>
+      <c r="F134" s="4" t="inlineStr"/>
       <c r="G134" s="4" t="n">
         <v>-449</v>
       </c>
@@ -31036,16 +30028,8 @@
           <t>前鼎</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>232.00</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t>-11.5</t>
-        </is>
-      </c>
+      <c r="E135" s="4" t="inlineStr"/>
+      <c r="F135" s="4" t="inlineStr"/>
       <c r="G135" s="4" t="n">
         <v>-437</v>
       </c>
@@ -31069,16 +30053,8 @@
           <t>磐亞</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>29.10</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>+1.1</t>
-        </is>
-      </c>
+      <c r="E136" s="4" t="inlineStr"/>
+      <c r="F136" s="4" t="inlineStr"/>
       <c r="G136" s="4" t="n">
         <v>-436</v>
       </c>
@@ -31102,16 +30078,8 @@
           <t>雍智科技</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>1675.00</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>+5.0</t>
-        </is>
-      </c>
+      <c r="E137" s="4" t="inlineStr"/>
+      <c r="F137" s="4" t="inlineStr"/>
       <c r="G137" s="4" t="n">
         <v>-402</v>
       </c>
@@ -31135,16 +30103,8 @@
           <t>廣閎科</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>178.00</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>-5.5</t>
-        </is>
-      </c>
+      <c r="E138" s="4" t="inlineStr"/>
+      <c r="F138" s="4" t="inlineStr"/>
       <c r="G138" s="4" t="n">
         <v>-401</v>
       </c>
@@ -31168,16 +30128,8 @@
           <t>旺矽</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>5495.00</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr">
-        <is>
-          <t>-305.0</t>
-        </is>
-      </c>
+      <c r="E139" s="4" t="inlineStr"/>
+      <c r="F139" s="4" t="inlineStr"/>
       <c r="G139" s="4" t="n">
         <v>-393</v>
       </c>
@@ -31201,16 +30153,8 @@
           <t>匯鑽科</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>64.40</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>+1.9</t>
-        </is>
-      </c>
+      <c r="E140" s="4" t="inlineStr"/>
+      <c r="F140" s="4" t="inlineStr"/>
       <c r="G140" s="4" t="n">
         <v>-369</v>
       </c>
@@ -31234,16 +30178,8 @@
           <t>九暘</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>83.50</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>+0.8</t>
-        </is>
-      </c>
+      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="inlineStr"/>
       <c r="G141" s="4" t="n">
         <v>-355</v>
       </c>
@@ -31267,16 +30203,8 @@
           <t>原相</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>184.00</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E142" s="4" t="inlineStr"/>
+      <c r="F142" s="4" t="inlineStr"/>
       <c r="G142" s="4" t="n">
         <v>-354</v>
       </c>
@@ -31300,16 +30228,8 @@
           <t>亞泰金屬</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>478.00</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr">
-        <is>
-          <t>-9.0</t>
-        </is>
-      </c>
+      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="inlineStr"/>
       <c r="G143" s="4" t="n">
         <v>-314</v>
       </c>
@@ -31333,16 +30253,8 @@
           <t>千附</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>67.00</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
       <c r="G144" s="4" t="n">
         <v>-291</v>
       </c>
@@ -31366,16 +30278,8 @@
           <t>聖暉*</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>865.00</t>
-        </is>
-      </c>
-      <c r="F145" s="4" t="inlineStr">
-        <is>
-          <t>-23.0</t>
-        </is>
-      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
       <c r="G145" s="4" t="n">
         <v>-289</v>
       </c>
@@ -31399,16 +30303,8 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>1235.00</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-15.0</t>
-        </is>
-      </c>
+      <c r="E146" s="4" t="inlineStr"/>
+      <c r="F146" s="4" t="inlineStr"/>
       <c r="G146" s="4" t="n">
         <v>-284</v>
       </c>
@@ -31432,16 +30328,8 @@
           <t>譜瑞-KY</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>567.00</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
+      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="inlineStr"/>
       <c r="G147" s="4" t="n">
         <v>-280</v>
       </c>
@@ -31465,16 +30353,8 @@
           <t>精測</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>3485.00</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>-35.0</t>
-        </is>
-      </c>
+      <c r="E148" s="4" t="inlineStr"/>
+      <c r="F148" s="4" t="inlineStr"/>
       <c r="G148" s="4" t="n">
         <v>-261</v>
       </c>
@@ -31498,16 +30378,8 @@
           <t>方土昶</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>48.50</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
+      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="n">
         <v>-260</v>
       </c>
@@ -31531,16 +30403,8 @@
           <t>晟田</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>60.70</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
+      <c r="E150" s="4" t="inlineStr"/>
+      <c r="F150" s="4" t="inlineStr"/>
       <c r="G150" s="4" t="n">
         <v>-257</v>
       </c>
@@ -31564,16 +30428,8 @@
           <t>元太</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>144.50</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr">
-        <is>
-          <t>-2.0</t>
-        </is>
-      </c>
+      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="inlineStr"/>
       <c r="G151" s="4" t="n">
         <v>-244</v>
       </c>
@@ -31597,16 +30453,8 @@
           <t>IET-KY</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>581.00</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="inlineStr"/>
+      <c r="F152" s="4" t="inlineStr"/>
       <c r="G152" s="4" t="n">
         <v>-243</v>
       </c>
@@ -31630,16 +30478,8 @@
           <t>金山電</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>113.50</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>+0.5</t>
-        </is>
-      </c>
+      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="inlineStr"/>
       <c r="G153" s="4" t="n">
         <v>-214</v>
       </c>
@@ -31663,16 +30503,8 @@
           <t>緯致</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>120.00</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
+      <c r="E154" s="4" t="inlineStr"/>
+      <c r="F154" s="4" t="inlineStr"/>
       <c r="G154" s="4" t="n">
         <v>-202</v>
       </c>
@@ -31696,16 +30528,8 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>2875.00</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>-5.0</t>
-        </is>
-      </c>
+      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="inlineStr"/>
       <c r="G155" s="4" t="n">
         <v>-196</v>
       </c>
@@ -31729,16 +30553,8 @@
           <t>中天</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E156" s="4" t="inlineStr"/>
+      <c r="F156" s="4" t="inlineStr"/>
       <c r="G156" s="4" t="n">
         <v>-192</v>
       </c>
@@ -31762,16 +30578,8 @@
           <t>榮剛</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>+0.05</t>
-        </is>
-      </c>
+      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="inlineStr"/>
       <c r="G157" s="4" t="n">
         <v>-183</v>
       </c>
@@ -31795,16 +30603,8 @@
           <t>宏碁資訊</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>256.50</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>-10.0</t>
-        </is>
-      </c>
+      <c r="E158" s="4" t="inlineStr"/>
+      <c r="F158" s="4" t="inlineStr"/>
       <c r="G158" s="4" t="n">
         <v>-180</v>
       </c>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -3939,17 +3939,17 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
@@ -3957,46 +3957,46 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>24, 29</t>
+          <t>24, 01</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1516</v>
+        <v>4403</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>30, 02</t>
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>-1045</v>
+        <v>-3932</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>471</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>[('neutral', '02'), ('sell', '01'), ('neutral', '30'), ('buy', '29'), ('buy', '24')]</t>
+          <t>[('sell', '02'), ('buy', '01'), ('sell', '30'), ('neutral', '29'), ('buy', '24')]</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
@@ -4004,29 +4004,29 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>24, 01</t>
+          <t>24, 29</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>4403</v>
+        <v>1516</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>30, 02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-3932</v>
+        <v>-1045</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>471</v>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>[('sell', '02'), ('buy', '01'), ('sell', '30'), ('neutral', '29'), ('buy', '24')]</t>
+          <t>[('neutral', '02'), ('sell', '01'), ('neutral', '30'), ('buy', '29'), ('buy', '24')]</t>
         </is>
       </c>
     </row>

--- a/StockInfo/otc_analysis_result.xlsx
+++ b/StockInfo/otc_analysis_result.xlsx
@@ -3939,17 +3939,17 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>鈦昇</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="D114" s="4" t="n">
@@ -3957,46 +3957,46 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>24, 01</t>
+          <t>24, 29</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>4403</v>
+        <v>1516</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>30, 02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>-3932</v>
+        <v>-1045</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>471</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
-          <t>[('sell', '02'), ('buy', '01'), ('sell', '30'), ('neutral', '29'), ('buy', '24')]</t>
+          <t>[('neutral', '02'), ('sell', '01'), ('neutral', '30'), ('buy', '29'), ('buy', '24')]</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>鈦昇</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>電機機械</t>
+          <t>電子零組件業</t>
         </is>
       </c>
       <c r="D115" s="4" t="n">
@@ -4004,29 +4004,29 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>24, 29</t>
+          <t>24, 01</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1516</v>
+        <v>4403</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>30, 02</t>
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>-1045</v>
+        <v>-3932</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>471</v>
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>[('neutral', '02'), ('sell', '01'), ('neutral', '30'), ('buy', '29'), ('buy', '24')]</t>
+          <t>[('sell', '02'), ('buy', '01'), ('sell', '30'), ('neutral', '29'), ('buy', '24')]</t>
         </is>
       </c>
     </row>
